--- a/data/trans_orig/IP31KM03_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM03_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47747</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42371</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51230</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>95,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>49235</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44431</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51919</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>41463</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46403</t>
+          <t>37438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55526</t>
+          <t>44068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>89209</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94592</t>
+          <t>82903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106101</t>
+          <t>93883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5968</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11344</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4464</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1780</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9268</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10576</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17451</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>383726</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>367455</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>398424</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>526</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>383238</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>368545</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>398491</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>84,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>81,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>88,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>417329</t>
+          <t>357176</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>400247</t>
+          <t>344115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>433821</t>
+          <t>370041</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>800567</t>
+          <t>740903</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>777990</t>
+          <t>719387</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>824293</t>
+          <t>760325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82697</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67999</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98968</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>68594</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53341</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83287</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>87921</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71429</t>
+          <t>54625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105003</t>
+          <t>80551</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>156515</t>
+          <t>150187</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132789</t>
+          <t>130765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179092</t>
+          <t>171703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142249</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>132050</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149514</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>85,34%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>79,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>119614</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>110870</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>126710</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>120606</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145154</t>
+          <t>112074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162297</t>
+          <t>127770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>274106</t>
+          <t>262855</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261390</t>
+          <t>251275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>284947</t>
+          <t>273751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24437</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17172</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34636</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>26572</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19476</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35316</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35985</t>
+          <t>35066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>50970</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>40074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65934</t>
+          <t>62550</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>573722</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>554146</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>590560</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>85,98%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>768</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>552087</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>533965</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>567974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>84,71%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>81,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519245</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>602396</t>
+          <t>503550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>642254</t>
+          <t>532952</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1176141</t>
+          <t>1092967</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1150483</t>
+          <t>1068520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1200338</t>
+          <t>1115550</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>113102</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96264</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>132678</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>99630</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>83743</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117752</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>120679</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>84759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142337</t>
+          <t>114161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>220309</t>
+          <t>211568</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196112</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245967</t>
+          <t>236015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
